--- a/artfynd/A 31397-2026 artfynd.xlsx
+++ b/artfynd/A 31397-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AZ51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495534</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495544</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495561</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495538</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495546</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495532</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495545</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495556</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495529</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495533</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495593</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1844,6 +1904,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495551</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1946,6 +2011,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495527</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2048,6 +2118,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495537</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2150,6 +2225,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495541</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2257,6 +2337,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495547</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2364,6 +2449,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495548</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2471,6 +2561,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495552</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2578,6 +2673,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495553</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2685,6 +2785,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495554</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2792,6 +2897,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495555</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2889,6 +2999,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495557</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2996,6 +3111,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495603</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3093,6 +3213,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495567</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3195,6 +3320,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495564</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3300,6 +3430,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495563</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3412,6 +3547,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495558</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3515,6 +3655,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495599</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3612,6 +3757,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495559</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3709,6 +3859,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495528</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3806,6 +3961,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495530</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3903,6 +4063,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495531</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4000,6 +4165,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495535</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4097,6 +4267,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495536</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4194,6 +4369,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495539</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4291,6 +4471,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495540</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4388,6 +4573,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495542</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4485,6 +4675,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495549</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4582,6 +4777,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495550</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4679,6 +4879,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495562</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4776,6 +4981,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495589</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4873,6 +5083,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495590</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4970,6 +5185,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495591</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5067,6 +5287,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495594</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5164,6 +5389,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495595</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5261,6 +5491,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495597</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5358,6 +5593,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495598</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5455,6 +5695,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495600</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5552,6 +5797,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495601</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5649,8 +5899,65 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495604</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 31397-2026 artfynd.xlsx
+++ b/artfynd/A 31397-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135495534</v>
       </c>
       <c r="B2" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135495544</v>
       </c>
       <c r="B3" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135495561</v>
       </c>
       <c r="B4" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135495538</v>
       </c>
       <c r="B5" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135495546</v>
       </c>
       <c r="B6" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135495532</v>
       </c>
       <c r="B7" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135495545</v>
       </c>
       <c r="B8" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135495556</v>
       </c>
       <c r="B9" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135495529</v>
       </c>
       <c r="B10" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135495533</v>
       </c>
       <c r="B11" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135495593</v>
       </c>
       <c r="B12" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135495551</v>
       </c>
       <c r="B13" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135495527</v>
       </c>
       <c r="B14" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>135495537</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>135495541</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>135495547</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>135495548</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>135495552</v>
       </c>
       <c r="B19" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>135495553</v>
       </c>
       <c r="B20" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>135495554</v>
       </c>
       <c r="B21" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>135495555</v>
       </c>
       <c r="B22" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>135495557</v>
       </c>
       <c r="B23" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>135495603</v>
       </c>
       <c r="B24" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>135495567</v>
       </c>
       <c r="B25" t="n">
-        <v>58410</v>
+        <v>58415</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>135495564</v>
       </c>
       <c r="B26" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>135495563</v>
       </c>
       <c r="B27" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>135495558</v>
       </c>
       <c r="B28" t="n">
-        <v>58839</v>
+        <v>58844</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>135495599</v>
       </c>
       <c r="B29" t="n">
-        <v>40305</v>
+        <v>40308</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>135495559</v>
       </c>
       <c r="B30" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>135495528</v>
       </c>
       <c r="B31" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>135495530</v>
       </c>
       <c r="B32" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>135495531</v>
       </c>
       <c r="B33" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>135495535</v>
       </c>
       <c r="B34" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>135495536</v>
       </c>
       <c r="B35" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>135495539</v>
       </c>
       <c r="B36" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>135495540</v>
       </c>
       <c r="B37" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>135495542</v>
       </c>
       <c r="B38" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>135495549</v>
       </c>
       <c r="B39" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>135495550</v>
       </c>
       <c r="B40" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>135495562</v>
       </c>
       <c r="B41" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>135495589</v>
       </c>
       <c r="B42" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>135495590</v>
       </c>
       <c r="B43" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>135495591</v>
       </c>
       <c r="B44" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>135495594</v>
       </c>
       <c r="B45" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>135495595</v>
       </c>
       <c r="B46" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>135495597</v>
       </c>
       <c r="B47" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135495598</v>
       </c>
       <c r="B48" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>135495600</v>
       </c>
       <c r="B49" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>135495601</v>
       </c>
       <c r="B50" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>135495604</v>
       </c>
       <c r="B51" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 31397-2026 artfynd.xlsx
+++ b/artfynd/A 31397-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135495534</v>
       </c>
       <c r="B2" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135495544</v>
       </c>
       <c r="B3" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135495561</v>
       </c>
       <c r="B4" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135495538</v>
       </c>
       <c r="B5" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135495546</v>
       </c>
       <c r="B6" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135495532</v>
       </c>
       <c r="B7" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135495545</v>
       </c>
       <c r="B8" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135495556</v>
       </c>
       <c r="B9" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135495529</v>
       </c>
       <c r="B10" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135495533</v>
       </c>
       <c r="B11" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135495593</v>
       </c>
       <c r="B12" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>135495559</v>
       </c>
       <c r="B30" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>135495528</v>
       </c>
       <c r="B31" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>135495530</v>
       </c>
       <c r="B32" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>135495531</v>
       </c>
       <c r="B33" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>135495535</v>
       </c>
       <c r="B34" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>135495536</v>
       </c>
       <c r="B35" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>135495539</v>
       </c>
       <c r="B36" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>135495540</v>
       </c>
       <c r="B37" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>135495542</v>
       </c>
       <c r="B38" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>135495549</v>
       </c>
       <c r="B39" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>135495550</v>
       </c>
       <c r="B40" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>135495562</v>
       </c>
       <c r="B41" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>135495589</v>
       </c>
       <c r="B42" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>135495590</v>
       </c>
       <c r="B43" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>135495591</v>
       </c>
       <c r="B44" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>135495594</v>
       </c>
       <c r="B45" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>135495595</v>
       </c>
       <c r="B46" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>135495597</v>
       </c>
       <c r="B47" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135495598</v>
       </c>
       <c r="B48" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>135495600</v>
       </c>
       <c r="B49" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>135495601</v>
       </c>
       <c r="B50" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>135495604</v>
       </c>
       <c r="B51" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 31397-2026 artfynd.xlsx
+++ b/artfynd/A 31397-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135495534</v>
       </c>
       <c r="B2" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135495544</v>
       </c>
       <c r="B3" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135495561</v>
       </c>
       <c r="B4" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135495538</v>
       </c>
       <c r="B5" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135495546</v>
       </c>
       <c r="B6" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135495532</v>
       </c>
       <c r="B7" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135495545</v>
       </c>
       <c r="B8" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135495556</v>
       </c>
       <c r="B9" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>135495559</v>
       </c>
       <c r="B30" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>135495528</v>
       </c>
       <c r="B31" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>135495530</v>
       </c>
       <c r="B32" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>135495531</v>
       </c>
       <c r="B33" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>135495535</v>
       </c>
       <c r="B34" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>135495536</v>
       </c>
       <c r="B35" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>135495539</v>
       </c>
       <c r="B36" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>135495540</v>
       </c>
       <c r="B37" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>135495542</v>
       </c>
       <c r="B38" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>135495549</v>
       </c>
       <c r="B39" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>135495550</v>
       </c>
       <c r="B40" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>135495562</v>
       </c>
       <c r="B41" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>135495589</v>
       </c>
       <c r="B42" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>135495590</v>
       </c>
       <c r="B43" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>135495591</v>
       </c>
       <c r="B44" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>135495594</v>
       </c>
       <c r="B45" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>135495595</v>
       </c>
       <c r="B46" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>135495597</v>
       </c>
       <c r="B47" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135495598</v>
       </c>
       <c r="B48" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>135495600</v>
       </c>
       <c r="B49" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>135495601</v>
       </c>
       <c r="B50" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>135495604</v>
       </c>
       <c r="B51" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 31397-2026 artfynd.xlsx
+++ b/artfynd/A 31397-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135495534</v>
       </c>
       <c r="B2" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135495544</v>
       </c>
       <c r="B3" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135495561</v>
       </c>
       <c r="B4" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135495538</v>
       </c>
       <c r="B5" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135495546</v>
       </c>
       <c r="B6" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135495532</v>
       </c>
       <c r="B7" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135495545</v>
       </c>
       <c r="B8" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135495556</v>
       </c>
       <c r="B9" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135495529</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135495533</v>
       </c>
       <c r="B11" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135495593</v>
       </c>
       <c r="B12" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135495551</v>
       </c>
       <c r="B13" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135495527</v>
       </c>
       <c r="B14" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>135495537</v>
       </c>
       <c r="B15" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>135495541</v>
       </c>
       <c r="B16" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>135495547</v>
       </c>
       <c r="B17" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>135495548</v>
       </c>
       <c r="B18" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>135495552</v>
       </c>
       <c r="B19" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>135495553</v>
       </c>
       <c r="B20" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>135495554</v>
       </c>
       <c r="B21" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>135495555</v>
       </c>
       <c r="B22" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>135495557</v>
       </c>
       <c r="B23" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>135495603</v>
       </c>
       <c r="B24" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>135495567</v>
       </c>
       <c r="B25" t="n">
-        <v>58415</v>
+        <v>58417</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>135495564</v>
       </c>
       <c r="B26" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>135495563</v>
       </c>
       <c r="B27" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>135495558</v>
       </c>
       <c r="B28" t="n">
-        <v>58844</v>
+        <v>58846</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>135495599</v>
       </c>
       <c r="B29" t="n">
-        <v>40308</v>
+        <v>40310</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>135495559</v>
       </c>
       <c r="B30" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>135495528</v>
       </c>
       <c r="B31" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>135495530</v>
       </c>
       <c r="B32" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>135495531</v>
       </c>
       <c r="B33" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>135495535</v>
       </c>
       <c r="B34" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>135495536</v>
       </c>
       <c r="B35" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>135495539</v>
       </c>
       <c r="B36" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>135495540</v>
       </c>
       <c r="B37" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>135495542</v>
       </c>
       <c r="B38" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>135495549</v>
       </c>
       <c r="B39" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>135495550</v>
       </c>
       <c r="B40" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>135495562</v>
       </c>
       <c r="B41" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>135495589</v>
       </c>
       <c r="B42" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>135495590</v>
       </c>
       <c r="B43" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>135495591</v>
       </c>
       <c r="B44" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>135495594</v>
       </c>
       <c r="B45" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>135495595</v>
       </c>
       <c r="B46" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>135495597</v>
       </c>
       <c r="B47" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135495598</v>
       </c>
       <c r="B48" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>135495600</v>
       </c>
       <c r="B49" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>135495601</v>
       </c>
       <c r="B50" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>135495604</v>
       </c>
       <c r="B51" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 31397-2026 artfynd.xlsx
+++ b/artfynd/A 31397-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135495534</v>
       </c>
       <c r="B2" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135495544</v>
       </c>
       <c r="B3" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135495561</v>
       </c>
       <c r="B4" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135495538</v>
       </c>
       <c r="B5" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135495546</v>
       </c>
       <c r="B6" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135495532</v>
       </c>
       <c r="B7" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135495545</v>
       </c>
       <c r="B8" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135495556</v>
       </c>
       <c r="B9" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135495529</v>
       </c>
       <c r="B10" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135495533</v>
       </c>
       <c r="B11" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135495593</v>
       </c>
       <c r="B12" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>135495559</v>
       </c>
       <c r="B30" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>135495528</v>
       </c>
       <c r="B31" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>135495530</v>
       </c>
       <c r="B32" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>135495531</v>
       </c>
       <c r="B33" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>135495535</v>
       </c>
       <c r="B34" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>135495536</v>
       </c>
       <c r="B35" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>135495539</v>
       </c>
       <c r="B36" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>135495540</v>
       </c>
       <c r="B37" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>135495542</v>
       </c>
       <c r="B38" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>135495549</v>
       </c>
       <c r="B39" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>135495550</v>
       </c>
       <c r="B40" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>135495562</v>
       </c>
       <c r="B41" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>135495589</v>
       </c>
       <c r="B42" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>135495590</v>
       </c>
       <c r="B43" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>135495591</v>
       </c>
       <c r="B44" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>135495594</v>
       </c>
       <c r="B45" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>135495595</v>
       </c>
       <c r="B46" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>135495597</v>
       </c>
       <c r="B47" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135495598</v>
       </c>
       <c r="B48" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>135495600</v>
       </c>
       <c r="B49" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>135495601</v>
       </c>
       <c r="B50" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>135495604</v>
       </c>
       <c r="B51" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
